--- a/artfynd/S 2326-2022 artfynd.xlsx
+++ b/artfynd/S 2326-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY84"/>
+  <dimension ref="A1:AZ84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -795,6 +800,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3878619</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -911,6 +921,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/429070</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1027,6 +1042,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/429071</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1143,6 +1163,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/429076</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1259,6 +1284,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/429380</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1375,6 +1405,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/429381</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1491,6 +1526,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/429382</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1607,6 +1647,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/429383</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1723,6 +1768,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/429384</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1839,6 +1889,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/429385</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1955,6 +2010,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/429387</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2071,6 +2131,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/429388</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2187,6 +2252,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/429389</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2318,6 +2388,11 @@
           <t>Åtgärdsprogram hällebräcka</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/430316</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2429,6 +2504,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/437636</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2540,6 +2620,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/437637</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2651,6 +2736,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/440288</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2762,6 +2852,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/440291</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2873,6 +2968,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56070524</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2989,6 +3089,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56070532</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3119,6 +3224,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56070534</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3240,6 +3350,11 @@
           <t>Studie av mellanårsvariation av groning hos hällebräcka, Saxifraga osloensis</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56522680</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3361,6 +3476,11 @@
           <t>Studie av mellanårsvariation av groning hos hällebräcka, Saxifraga osloensis</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56522710</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3478,6 +3598,11 @@
           <t>Studie av mellanårsvariation av groning hos hällebräcka, Saxifraga osloensis</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56523116</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3597,6 +3722,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77907795</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3709,6 +3839,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78179349</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3821,6 +3956,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78179351</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3933,6 +4073,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78179355</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4048,6 +4193,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93608222</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4150,6 +4300,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100980570</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4264,6 +4419,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116653006</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4370,6 +4530,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116653043</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4486,6 +4651,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128620274</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4584,6 +4754,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133433153</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4699,6 +4874,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126297045</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4810,6 +4990,11 @@
           <t>Länsstyrelsen i Örebro läns floraregister</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2830304</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4939,6 +5124,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2844955</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5050,6 +5240,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94690911</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5161,6 +5356,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110709391</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5268,6 +5468,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110710540</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5385,6 +5590,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110883328</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5493,6 +5703,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110883342</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5601,6 +5816,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110883392</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5709,6 +5929,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110883594</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5826,6 +6051,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110884108</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5943,6 +6173,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110884193</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6064,6 +6299,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110884225</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6172,6 +6412,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110884328</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6280,6 +6525,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110884843</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6391,6 +6641,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118442949</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6488,6 +6743,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118443830</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6595,6 +6855,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110708941</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6702,6 +6967,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110710304</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6813,6 +7083,11 @@
           <t>Länsstyrelsen i Örebro läns floraregister</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2845136</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6928,6 +7203,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78381742</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7026,6 +7306,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110709035</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7137,6 +7422,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110710621</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7243,6 +7533,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118443821</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7354,6 +7649,11 @@
           <t>Länsstyrelsen i Örebro läns floraregister</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2667760</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7460,6 +7760,11 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57265888</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7571,6 +7876,11 @@
           <t>Länsstyrelsen i Örebro läns floraregister</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2566380</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7691,6 +8001,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2591256</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7802,6 +8117,11 @@
           <t>Länsstyrelsen i Örebro läns floraregister</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3357211</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7900,6 +8220,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110710724</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8020,6 +8345,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4426485</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8128,6 +8458,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110883356</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8225,6 +8560,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77848868</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8336,6 +8676,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110708522</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8444,6 +8789,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110882851</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8552,6 +8902,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110883568</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8660,6 +9015,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110884234</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8768,6 +9128,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110884644</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8865,6 +9230,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118443026</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8962,6 +9332,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118443995</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9073,6 +9448,11 @@
           <t>Länsstyrelsen i Örebro läns floraregister</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5028061</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9193,6 +9573,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5048542</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9305,6 +9690,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78179350</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9416,6 +9806,11 @@
           <t>Länsstyrelsen i Örebro läns floraregister</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5218537</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9513,6 +9908,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77848869</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9611,6 +10011,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110708617</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9723,6 +10128,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126285775</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9834,6 +10244,11 @@
           <t>Länsstyrelsen i Örebro läns floraregister</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6417694</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9939,8 +10354,98 @@
           <t>Närkes Flora 2013</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88007247</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>